--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -676,7 +676,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -722,10 +722,22 @@
           <t>Metronome 120 in one earbud. Count "one two three four five six seven eight" — one number per click, normal teaching voice. Repeat the 1–8 round FOUR times without stopping (~20 seconds total). Say nothing else before, during, or after.</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr"/>
-      <c r="O4" s="7" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06 bounce. System: 122.2 BPM ✓, counts 8 ✓, but heard 4/4 — flat accents make 2/4 vs 4/4 inaudible. Optional take 2 with clear ONE-two accents.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -1970,7 +1982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2067,70 +2079,77 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="41" customHeight="1">
       <c r="B15" s="10" t="inlineStr">
         <is>
+          <t>•  DO let your natural musical accents live — the ONE-two of a march, the lilt of a waltz. Accents aren't label-leaking; they're the very thing the system must learn to hear (clip 1 taught us this: flat counting made 2/4 indistinguishable from 4/4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
           <t>•  A recording went wrong? Don't delete — record again and write 'take 2' in Take notes.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="10" t="inlineStr"/>
-    </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Reading the sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>•  White cells are pre-filled suggestions: BPM and counts you're welcome to change — if you do, put the real values in the yellow Actual columns.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>•  Yellow cells are yours to fill in after each clip.</t>
+          <t>•  White cells are pre-filled suggestions: BPM and counts you're welcome to change — if you do, put the real values in the yellow Actual columns.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>•  Row 2 of the Recordings tab is a grayed-out example of a finished row.</t>
+          <t>•  Yellow cells are yours to fill in after each clip.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="B21" s="10" t="inlineStr">
         <is>
+          <t>•  Row 2 of the Recordings tab is a grayed-out example of a finished row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
           <t>•  ★ in the Pri column = the ten most valuable clips.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="10" t="inlineStr"/>
-    </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Files</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>•  Name each memo with the row's Filename if it's easy; otherwise just keep the memos in row order — the sheet is the source of truth.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>•  Name each memo with the row's Filename if it's easy; otherwise just keep the memos in row order — the sheet is the source of truth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>•  When done, send the memos plus this sheet (or a photo of it) back.</t>
         </is>

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -739,7 +739,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
@@ -789,10 +789,22 @@
           <t>Metronome 90. Count a waltz combination exactly the way you naturally count one — in 3s, in 6s, or across 8 — your habit IS the data. Three or four rounds. Then write in 'Actual counts' precisely how you counted one phrase (e.g. "counted 1-2-3 4-2-3, phrase = 8 bars").</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="7" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07. Counted 'ONE-and-ah' 1-8 ×4, click on numbers. System: counts 8 ✓; final tempo 108/4-4 ✗ BUT Gemini markers had 90.8 @ 92% and lost the fusion vote — key finding, see baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1982,7 +1994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="B1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -857,7 +857,7 @@
       <c r="N6" s="6" t="inlineStr"/>
       <c r="O6" s="7" t="inlineStr"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -907,10 +907,22 @@
           <t>Compound meter. Set the metronome to 100 and count the 6/8 bar as you would for class — "one two three four five six" or "ONE-and-a-TWO-and-a" — whichever is natural. Four rounds. Write EXACTLY what you spoke in 'Take notes' and confirm the phrase length in 'Actual counts'.</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="7" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07, take 2 (take 1 bounced silent). FIRST 6/8 recognized — accents worked. Onset tempo dragged to 84.7 by agogic bar-boundary gaps (spoke 96.3 on the 100 click); tempo row honestly red. Markers 96.3@51% under gate again.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="43" customHeight="1">
       <c r="A8" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
@@ -852,10 +852,22 @@
           <t>Same as clip 1 but metronome 104: count 1–8 four times through, one number per click, nothing else on the recording.</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07. FIRST ALL-GREEN ROW: 102.3 (1.6%), 4/4, 8 counts, none — all correct. Control confirms clip 4's tempo miss was accent-induced. Clean headroom this time.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -936,7 +936,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="43" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
@@ -982,10 +982,22 @@
           <t>No numbers anywhere in this one. Mark a simple 8-count exercise with step names only — "tendu front, and close, brush through, and side…" — each key word landing on a click. Two or three times through.</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
-      <c r="N8" s="6" t="inlineStr"/>
-      <c r="O8" s="7" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07. Step names only, 4 rounds of 8; some counts left silent (no word every click) by design. Pipeline read 77.8 BPM / 4/4 / 16 counts — all wrong. Root cause: Gemini numbers every spoken word as a consecutive beat with no notion of skipped counts, so sparse markers read as slower tempo and fewer counts. New failure mode vs clip 4 (sparse markers, not just uneven timing).</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="43" customHeight="1">
       <c r="A9" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -999,7 +999,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="43" customHeight="1">
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
@@ -1049,10 +1049,22 @@
           <t>Step names only, waltz feel, metronome 90. An 8-count balancé-ish phrase marked in words ("down and lift, and sway, and carry…"), two or three times through. No numbers at all.</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07. Step names, downbeat-stressed waltz, word on nearly every count. Pipeline read 130.2 BPM / 4/4 / 16 counts — all wrong. New variant of clip 2s waltz finding: onset (130.2) lands inside the 70-140 beat band so ADR-013 arbitration never engages, and Gemini only tagged the downbeat word of each bar as marker_type=beat (18 markers, 33.7 BPM, 57% confidence) -- near-bar-rate and just under the 60% arbitration gate. Neither signal path both correctly banded and correct.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1066,7 +1066,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
@@ -1112,10 +1112,22 @@
           <t>Step names only at 104 in 4/4 — a plié or tendu pattern, 8 counts, two or three times through, words on the beat, zero numbers.</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
-      <c r="N10" s="6" t="inlineStr"/>
-      <c r="O10" s="7" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07. Plie/tendu pattern, step names, mostly clean with a stray 8th-note syllable or two and one blank beat. Pipeline: 111.9 BPM (7.6% err, within 8% tolerance) - GREEN. Meter subdivision read duple vs true none (the stray syllables) - red. Counts 16 vs true 8 - same undercount pattern as clips 5-6.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="43" customHeight="1">
       <c r="A11" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1129,7 +1129,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="43" customHeight="1">
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
@@ -1175,10 +1175,22 @@
           <t>Step names only with the 6/8 swing at 100 — think pas de basque / skipping feel. One 6-count (or your natural) phrase, three times through. Confirm phrase length in 'Actual counts'.</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr"/>
-      <c r="O11" s="7" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07, take 2 (take 1 was the wrong exercise -- triplet-over-8, replaced after clarifying the 6/8 assignment in chat). IN-and-[ah] OUT-and-[ah] per bar, but only 4 of 6 syllables spoken (ahs silent), same silent-count pattern as clips 5-7. Bar-to-bar timing still close to the true 3.6s grid. Pipeline: 134.6 BPM (raw 67.3 x2), meter defaulted to 4/4, counts abstained (evidence disagreed) - all red. Sibling to clip 4s finding but meter recognition itself fails here.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="inlineStr">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1199,7 +1199,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="75" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
@@ -1249,10 +1249,22 @@
           <t>Count 1–8 once cleanly. Midway through the SECOND round, stop and explain something for about five seconds exactly like in class ("really lengthen through that arm, don't grip the barre") — then pick the counting back up and finish, plus one more clean round. The interruption is the point.</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr"/>
-      <c r="O13" s="7" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07. Clean round 1, ~5s in-tempo teaching interruption around count 3 of round 2, then resumed plus one more clean round. Pipeline: tempo 99.7 (4.1% err) and meter 4/4 both GREEN -- interruption didnt break tempo/meter tracking at all. Counts abstained (evidence disagreed) -- the interruption split the phrase and the two count signals disagreed, arguably the honest answer.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="43" customHeight="1">
       <c r="A14" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1266,7 +1266,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="43" customHeight="1">
+    <row r="14" ht="75" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
@@ -1312,10 +1312,22 @@
           <t>Same interruption trick but marking with step names only: mark the phrase once, stop mid-second-time to coach for ~5 seconds, then resume marking to the end.</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
-      <c r="N14" s="6" t="inlineStr"/>
-      <c r="O14" s="7" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07. Step names, word on every count (no gaps), interruption mid-second-round. Pipeline: tempo 104.8 (0.8% err) - GREEN, tightest yet on an interruption clip; dense markers held through the interruption. Meter subdivision duple vs true none - red. Counts 12 vs true 8 - red (clip 9 abstained here instead of committing wrong).</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="43" customHeight="1">
       <c r="A15" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1329,7 +1329,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="43" customHeight="1">
+    <row r="15" ht="75" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
@@ -1375,10 +1375,22 @@
           <t>In tempo, give the preparation first — "five, six, seven, eight" — then count 1–8 twice through. 'Counts per phrase' stays 8: the prep is NOT part of the phrase (that boundary is what we're testing).</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07. In-tempo prep (5,6,7,8) then 1-8 twice through, prep excluded from the phrase. Pipeline: tempo 103.9 (0.1% err), meter 4/4, subdivision none, counts 8 - ALL GREEN. Prep-vs-phrase boundary correctly excluded. Oddity: structure also reported 2 side(s) though this is one-side (not scored, not in expect block).</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1392,7 +1392,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="90" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
@@ -1442,10 +1442,22 @@
           <t>The quick-reminder voice. Pick an exercise you'd RUN at 120, set the metronome to 60, and mark it at that half speed the way you would when time is short. Metronome column already says 60 (what you speak); write "intended 120" in 'Take notes' (or your actual pair if you chose different numbers).</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr"/>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. Deliberately slow quick-reminder voice (intended 120, spoken at 60), 2 clean rounds of 8, no gaps. Pipeline: raw onset read 62.2 BPM at 100% coverage, CV=0.00 (near-perfect, essentially exact) but got doubled to 124.4 by the low-tempo x2 band-normalization heuristic (named failure_mode=metric_level_x2 in the scorer) - RED. Counts (8) correct. Cleanest case yet of the multiplier bug also seen on clips 6 and 8 - the checklists purpose-built half-tempo probe found exactly what it was designed to find.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="69" customHeight="1">
       <c r="A17" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1459,7 +1459,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="69" customHeight="1">
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
@@ -1509,10 +1509,22 @@
           <t>THE most valuable clip on this sheet. A long, fast, frappé-style combination — 32 to 64 counts — marked with step names at speed (metronome 160, or 80 if you prefer feeling it in twos: note which in 'Take notes'). Write the exact phrase length you used in 'Actual counts'. This is the shape the system currently cannot crack.</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. Fast frappe-style, step names, 8 fast sets of 8 (64 counts). Pipeline: raw onset 161.8 BPM at 83% conf/100% coverage/CV=0.05 - essentially exact (1.1% err) - but band-snap halved it to 80.9 (4/4 duple) because 161.8 sits just above the 140 ceiling. Mirror image of clip 12s finding (ADR-014): too-fast instead of too-slow, same defect. Meter got equivalent_reading partial credit (0.5) via existing surface equivalence logic; tempo scored flatly wrong - the exact scoring inconsistency ADR-014 flags as follow-on work. Counts 32 vs true 64.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1526,7 +1526,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="105" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
@@ -1572,10 +1572,22 @@
           <t>Slow sustained adagio marking at 63 — long vowels, connected words ("développééé… aaand carry… fondu dooown…"). One 8-count phrase, twice through.</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
-      <c r="N18" s="6" t="inlineStr"/>
-      <c r="O18" s="7" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. Slow sustained adagio, long vowels/connected words, 8-count phrase x4 rounds. Pipeline: tempo 92.2 (46% err) - RED, but NOT the ADR-014 band-snap defect (92.2 isnt a clean x2/x3 of 63, and it already sits inside 70-140). Gemini found no beats at all (fully abstained). Likely the sustained/legato delivery confuses onset word-boundary segmentation directly - local sections read 92/54/94 BPM with CV up to 0.36, vs CV 0.00-0.07 on clipped/counted takes. Counts abstained.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1589,7 +1589,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="90" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
@@ -1639,10 +1639,22 @@
           <t>Metronome 80. Count with triplet subdivision — "ONE-and-a-TWO-and-a-THREE-and-a…" — numbers on the clicks, the little syllables evenly between them. Two rounds of 8. (This subdivision is a known machine-breaker — keep it steady.)</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. ONE-and-a-TWO-and-a triplet subdivision, numbers, 2 rounds of 8. Pipeline: tempo 80.8 (1.0% err), meter 4/4 triplet, counts 8 - ALL GREEN. Marker path (80.8, 90% conf, 16 beats) correctly outvoted the syllable-level onset (186.9, outside band) - real-world confirmation of ADR-013 band-aware arbitration on the exact clip type it was built to fix. Third all-green rig row (after clips 3, 11).</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="43" customHeight="1">
       <c r="A20" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1656,7 +1656,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="43" customHeight="1">
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
@@ -1702,10 +1702,22 @@
           <t>Metronome 104. Count with eighth-note subdivision — "ONE-and-TWO-and-THREE-and…" — numbers on the clicks, "and" exactly halfway between. Two rounds of 8.</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr"/>
-      <c r="M20" s="6" t="inlineStr"/>
-      <c r="N20" s="6" t="inlineStr"/>
-      <c r="O20" s="7" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. ONE-and-TWO-and eighth-note (duple) subdivision, numbers, 2 rounds of 8. Pipeline: tempo 102.9 (1.1% err), meter 4/4 duple, counts 8 - ALL GREEN. Marker path (102.9, 92% conf) again outvoted the syllable-level onset (216.3). Aside: the separate raw SubdivisionResult misread triplet at 100% conf, but that path is unused by scoring - only the arbitrated coherent answer counts. Fifth all-green rig row (clips 3, 11, 15).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="105" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>17</v>
       </c>
@@ -1772,10 +1772,22 @@
           <t>Mark with sounds instead of words — "da da DA da… and da-da… TA" — however you naturally vocalize a phrase. Any meter is fine: the sheet suggests 4/4 at 100, but if you change it, correct the Meter/'Actual BPM' cells. 8-count phrase, three times through.</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr"/>
-      <c r="N22" s="6" t="inlineStr"/>
-      <c r="O22" s="7" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. Vocables ("da da DA da" style) with intentional duple subdivision, 2 rounds of 8. Pipeline: tempo 99.5 (0.5% err), meter 4/4 duple, counts 8 - ALL GREEN on the numbers. BUT: Whispers transcript hallucinated literal number-words (one and two three...) instead of the actual vocable sounds - almost certainly the ballet-vocabulary prompt biasing transcription. Timing survived so scoring passed, but the literal transcript is fabricated - a distinct hallucination defect worth its own investigation. Sixth all-green rig row.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1789,7 +1789,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="90" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>18</v>
       </c>
@@ -1839,10 +1839,22 @@
           <t>Count FOUR rounds of 1-to-8 that together form ONE 32-count combination — think of it as one long exercise, four eights. 'Counts per phrase' is already set to 32, NOT 8: machines hear four cycles of eight, and whether they realize it's one phrase is exactly the test.</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr"/>
-      <c r="O23" s="7" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. Four rounds of 1-8, different inflections, meant as ONE 32-count combination. Pipeline: tempo 104.9 (0.9% err) and meter 4/4 both correct. Structure read 8 counts vs true 32 - the expected finding: the system hears four cycles of eight with no signal they form one longer phrase. Distinct from clips 5-8s sparse-marker undercount - every count was spoken cleanly here; this is a pure phrase-boundary/grouping miss.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="43" customHeight="1">
       <c r="A24" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1856,7 +1856,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="43" customHeight="1">
+    <row r="24" ht="90" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>19</v>
       </c>
@@ -1902,10 +1902,22 @@
           <t>Same 32-count idea as clip 18: count it through once, say "other side", and count it through again. Sides = both, counts stay 32 (one side's phrase — sides are never multiplied into counts).</t>
         </is>
       </c>
-      <c r="L24" s="6" t="inlineStr"/>
-      <c r="M24" s="6" t="inlineStr"/>
-      <c r="N24" s="6" t="inlineStr"/>
-      <c r="O24" s="7" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. 32 counts, "other side" spoken between rounds, 32 counts again (numbering resets). Pipeline: tempo 104.1 (0.1% err) and meter 4/4 both correct. Sides correctly read 2 - the other side cue worked. Counts read 8 vs true 32 - same phrase-boundary miss as clip 18. Interesting split: side-detection succeeded where phrase-length grouping failed on the same underlying shape.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="43" customHeight="1">
       <c r="A25" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="105" customHeight="1">
+    <row r="22" ht="120" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>17</v>
       </c>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08. Vocables ("da da DA da" style) with intentional duple subdivision, 2 rounds of 8. Pipeline: tempo 99.5 (0.5% err), meter 4/4 duple, counts 8 - ALL GREEN on the numbers. BUT: Whispers transcript hallucinated literal number-words (one and two three...) instead of the actual vocable sounds - almost certainly the ballet-vocabulary prompt biasing transcription. Timing survived so scoring passed, but the literal transcript is fabricated - a distinct hallucination defect worth its own investigation. Sixth all-green rig row.</t>
+          <t>2026-08-08, re-exported after Ben found the original bounce had two overlapping tracks (label unchanged: 100bpm, 4/4, duple, 8 counts x2). The corrected export FLIPS the finding: original (overlapping) export had Whisper hallucinate a clean one-and-two-three... transcript, so tempo/meter/counts scored all-green by accident. The fixed, clean export shows Whisper collapsing the whole 9.5s vocable phrase into ONE un-timestamped blob (da-da-da-hoo-ha-hee...) - zero per-syllable timing, so everything now abstains. More fundamental defect than the original hallucination: Whisper doesnt segment non-lexical bursts into timed tokens at all.</t>
         </is>
       </c>
     </row>

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1919,7 +1919,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="43" customHeight="1">
+    <row r="25" ht="105" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>20</v>
       </c>
@@ -1969,10 +1969,22 @@
           <t>A waltz with real LILT — let your voice swing the downbeat ("DOWN two three, LIFT two three…"), balancé feel, metronome 88. 8 or 16 counts (write which in 'Actual counts'), two or three times through.</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr"/>
-      <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr"/>
-      <c r="O25" s="7" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. Step names, downbeat lilt (DOWN two three, LIFT two three), one word per click no subdivision, 8 counts. Pipeline: tempo 91.6 (4.1% err) - GREEN. Meter read 4/4 duple vs true 3/4 none - another waltz-precedence instance (clips 6, 13). Near-miss: marker path read 90.6 BPM at 59% confidence - one point under ADR-013s 60% arbitration gate. Had it cleared, the correct in-band marker reading would have won. Counts 24 vs true 8.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="43" customHeight="1">
       <c r="A26" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -1986,7 +1986,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="43" customHeight="1">
+    <row r="26" ht="105" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>21</v>
       </c>
@@ -2032,10 +2032,22 @@
           <t>Grand-allegro energy: big, sharp, accented marking — "and GRAND jeté, and RUN run RUN, and assemblé…" — full voice, 8 to 16 counts. Note the length in 'Actual counts'.</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr"/>
-      <c r="M26" s="6" t="inlineStr"/>
-      <c r="N26" s="6" t="inlineStr"/>
-      <c r="O26" s="7" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. Grand-allegro energy, big full-voice accents on jumps, 32 counts, mixed step-name bursts and counted numbers. Pipeline: tempo 115.1 (19.9% err) - RED, not a clean x2/x3 metric-level ratio, first section nearly perfectly steady (CV=0.00) at that faster tempo - reads as real tempo drift (energy/excitement rushing ahead of click), not a detection artifact. Meter follows the wrong tempo. Counts abstained - phrase mixes styles rather than one uniform pattern.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="56" customHeight="1">
       <c r="A27" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="105" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>22</v>
       </c>
@@ -2099,10 +2099,22 @@
           <t>The trap clip. Mark with step names but use numbers as AMOUNTS, never as counts: "we take TWO tendus front, ONE more, and THREE quick ones to the side…". Speak in tempo. The numbers must not line up with the count — that's what fools machines. Write the TRUE phrase length in 'Actual counts'.</t>
         </is>
       </c>
-      <c r="L27" s="6" t="inlineStr"/>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr"/>
-      <c r="O27" s="7" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. The trap clip - numbers used only as quantities in natural step-name phrasing (we take two tendus front, then one to the back, three quick chates...), never as beat counts, true phrase 32 counts. Trap worked exactly as designed: Gemini found ZERO beat markers. Onset detector locked onto irregular word spacing, read 170 (halved to 85 by band-snap) - 18.3% miss. Counts correctly abstained. Also reported 2 sides though no other side cue exists - likely an artifact, not scored.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -2116,7 +2116,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" ht="105" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>23</v>
       </c>
@@ -2162,10 +2162,22 @@
           <t>End-of-day voice: quiet, low-energy, slightly mumbled marking of any simple exercise — still in tempo with the earbud. 8 counts, twice through.</t>
         </is>
       </c>
-      <c r="L28" s="6" t="inlineStr"/>
-      <c r="M28" s="6" t="inlineStr"/>
-      <c r="N28" s="6" t="inlineStr"/>
-      <c r="O28" s="7" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. End-of-day quiet/mumbled voice, 16 counts (bounce saved with truncated filename g-names-4-4-100-quiet.mp3, corrected on copy). Whisper transcript is only 12 tokens total (reverence, and then we close, and reverence, and now were done, yeah) - wholesale word loss from the quiet delivery, not just occasional gaps. Gemini found only 3 beats at 48% conf. Pipeline: tempo 119.3 (19.3% err), meter 4/4 duple, counts 8 vs true 16 - all RED, roughly half the phrase lost.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="43" customHeight="1">
       <c r="A29" s="4" t="n">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -2179,7 +2179,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="43" customHeight="1">
+    <row r="29" ht="120" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>24</v>
       </c>
@@ -2225,10 +2225,22 @@
           <t>Mark a 32-count phrase, then finish FREELY with "aaand port de bras… and balance…" as an ending outside the count. 'Counts per phrase' stays 32 — the ending is NOT included (whether the machine knows that is the test).</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr"/>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr"/>
-      <c r="O29" s="7" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08. 32-count phrase (turning around and then we drop... jump jump jump port de bras) then genuinely free out-of-tempo coda (the other way, and balance, and stop) with irregular pauses. Interesting partial success: onset section boundary (2.3-20.8s) lines up almost exactly with the true 32-count phrase length at 104bpm - correctly excluded the free coda. But tempo within that section still read low (72.2, 30.6% miss, CV=0.01) - descriptive phrasing doesnt put one word per click. Counts abstained. Final clip on the sheet - all 24 done.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/evals/capture-checklist.xlsx
+++ b/docs/evals/capture-checklist.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -932,7 +932,7 @@
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07, take 2 (take 1 bounced silent). FIRST 6/8 recognized — accents worked. Onset tempo dragged to 84.7 by agogic bar-boundary gaps (spoke 96.3 on the 100 click); tempo row honestly red. Markers 96.3@51% under gate again.</t>
+          <t>2026-08-07, take 2 (take 1 bounced silent). FIRST 6/8 recognized — accents worked. Onset tempo dragged to 84.7 by agogic bar-boundary gaps (spoke 96.3 on the 100 click); tempo row honestly red. Markers 96.3@51% under gate again. ADR-015: tempo flipped GREEN (grid-fit rescued the agogic read) — meter triple with it.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08. Step names, downbeat lilt (DOWN two three, LIFT two three), one word per click no subdivision, 8 counts. Pipeline: tempo 91.6 (4.1% err) - GREEN. Meter read 4/4 duple vs true 3/4 none - another waltz-precedence instance (clips 6, 13). Near-miss: marker path read 90.6 BPM at 59% confidence - one point under ADR-013s 60% arbitration gate. Had it cleared, the correct in-band marker reading would have won. Counts 24 vs true 8.</t>
+          <t>2026-08-08. Step names, downbeat lilt (DOWN two three, LIFT two three), one word per click no subdivision, 8 counts. Pipeline: tempo 91.6 (4.1% err) - GREEN. Meter read 4/4 duple vs true 3/4 none - another waltz-precedence instance (clips 6, 13). Near-miss: marker path read 90.6 BPM at 59% confidence - one point under ADR-013s 60% arbitration gate. Had it cleared, the correct in-band marker reading would have won. Counts 24 vs true 8. ADR-015: tempo went red — genuinely ambiguous gaps (stretched beat vs two beats); the documented trade.</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08. Grand-allegro energy, big full-voice accents on jumps, 32 counts, mixed step-name bursts and counted numbers. Pipeline: tempo 115.1 (19.9% err) - RED, not a clean x2/x3 metric-level ratio, first section nearly perfectly steady (CV=0.00) at that faster tempo - reads as real tempo drift (energy/excitement rushing ahead of click), not a detection artifact. Meter follows the wrong tempo. Counts abstained - phrase mixes styles rather than one uniform pattern.</t>
+          <t>2026-08-08. Grand-allegro energy, big full-voice accents on jumps, 32 counts, mixed step-name bursts and counted numbers. Pipeline: tempo 115.1 (19.9% err) - RED, not a clean x2/x3 metric-level ratio, first section nearly perfectly steady (CV=0.00) at that faster tempo - reads as real tempo drift (energy/excitement rushing ahead of click), not a detection artifact. Meter follows the wrong tempo. Counts abstained - phrase mixes styles rather than one uniform pattern. ADR-015: flipped green by LUCK (words still lost); expect flip-back when ASR improves.</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08. End-of-day quiet/mumbled voice, 16 counts (bounce saved with truncated filename g-names-4-4-100-quiet.mp3, corrected on copy). Whisper transcript is only 12 tokens total (reverence, and then we close, and reverence, and now were done, yeah) - wholesale word loss from the quiet delivery, not just occasional gaps. Gemini found only 3 beats at 48% conf. Pipeline: tempo 119.3 (19.3% err), meter 4/4 duple, counts 8 vs true 16 - all RED, roughly half the phrase lost.</t>
+          <t>2026-08-08. End-of-day quiet/mumbled voice, 16 counts (bounce saved with truncated filename g-names-4-4-100-quiet.mp3, corrected on copy). Whisper transcript is only 12 tokens total (reverence, and then we close, and reverence, and now were done, yeah) - wholesale word loss from the quiet delivery, not just occasional gaps. Gemini found only 3 beats at 48% conf. Pipeline: tempo 119.3 (19.3% err), meter 4/4 duple, counts 8 vs true 16 - all RED, roughly half the phrase lost. ADR-015: flipped green by LUCK (words still lost); expect flip-back when ASR improves.</t>
         </is>
       </c>
     </row>
